--- a/tools/importer/reports/import-us-es.report.xlsx
+++ b/tools/importer/reports/import-us-es.report.xlsx
@@ -91,7 +91,7 @@
     <t>us-es</t>
   </si>
   <si>
-    <t>2026-08-07T10:53:29.974Z</t>
+    <t>2026-08-07T11:10:23.236Z</t>
   </si>
   <si>
     <t>Español</t>
